--- a/exports/trend_1d/PNBHOUSING_full_report.xlsx
+++ b/exports/trend_1d/PNBHOUSING_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>23.6</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42803</v>
+        <v>42804</v>
       </c>
       <c r="H2" t="n">
-        <v>812.65</v>
+        <v>798.2</v>
       </c>
       <c r="I2" t="n">
         <v>805.4867891819658</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K2" t="n">
-        <v>21.39</v>
+        <v>19.23</v>
       </c>
       <c r="L2" t="n">
         <v>1.48</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42809</v>
+        <v>42810</v>
       </c>
       <c r="H3" t="n">
-        <v>899.9</v>
+        <v>912.7</v>
       </c>
       <c r="I3" t="n">
         <v>902.7880316192632</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>-12.74</v>
+        <v>-14.34</v>
       </c>
       <c r="L3" t="n">
         <v>15.52</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>13.42</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42874</v>
+        <v>42877</v>
       </c>
       <c r="H4" t="n">
-        <v>1050.95</v>
+        <v>1029.4</v>
       </c>
       <c r="I4" t="n">
         <v>1030.799282922559</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K4" t="n">
-        <v>15.15</v>
+        <v>12.79</v>
       </c>
       <c r="L4" t="n">
         <v>2.34</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>14.78</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42885</v>
+        <v>42886</v>
       </c>
       <c r="H5" t="n">
-        <v>1131.85</v>
+        <v>1154.95</v>
       </c>
       <c r="I5" t="n">
         <v>1139.508905305116</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.949999999999999</v>
+        <v>-12.2</v>
       </c>
       <c r="L5" t="n">
-        <v>10.23</v>
+        <v>12.4</v>
       </c>
       <c r="M5" t="n">
         <v>4.01</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.94</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42937</v>
+        <v>42940</v>
       </c>
       <c r="H6" t="n">
-        <v>1245.15</v>
+        <v>1219.3</v>
       </c>
       <c r="I6" t="n">
         <v>1227.928579375176</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K6" t="n">
-        <v>7.81</v>
+        <v>5.57</v>
       </c>
       <c r="L6" t="n">
         <v>2.46</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>10.41</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42975</v>
+        <v>42976</v>
       </c>
       <c r="H7" t="n">
-        <v>1315.9</v>
+        <v>1325.7</v>
       </c>
       <c r="I7" t="n">
         <v>1323.970671388613</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.92</v>
+        <v>-8.73</v>
       </c>
       <c r="L7" t="n">
-        <v>9.029999999999999</v>
+        <v>11.54</v>
       </c>
       <c r="M7" t="n">
         <v>3.97</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>9.35</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H8" t="n">
-        <v>1294.55</v>
+        <v>1253.6</v>
       </c>
       <c r="I8" t="n">
         <v>1260.545642280347</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.35</v>
+        <v>-5.44</v>
       </c>
       <c r="L8" t="n">
-        <v>4.73</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
         <v>0.76</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.64</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43185</v>
+        <v>43186</v>
       </c>
       <c r="H9" t="n">
-        <v>978.15</v>
+        <v>1061.45</v>
       </c>
       <c r="I9" t="n">
         <v>1006.270391439306</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K9" t="n">
-        <v>21.97</v>
+        <v>15.33</v>
       </c>
       <c r="L9" t="n">
         <v>3.07</v>
@@ -954,7 +1061,7 @@
         <v>3.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.98</v>
+        <v>8.52</v>
       </c>
       <c r="O9" t="n">
         <v>-3.16</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>15.86</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="H10" t="n">
-        <v>1138.25</v>
+        <v>1047.85</v>
       </c>
       <c r="I10" t="n">
         <v>1072.156422385845</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K10" t="n">
-        <v>7.24</v>
+        <v>-1.28</v>
       </c>
       <c r="L10" t="n">
         <v>8.09</v>
       </c>
       <c r="M10" t="n">
-        <v>1.88</v>
+        <v>6.28</v>
       </c>
       <c r="N10" t="n">
-        <v>2.74</v>
+        <v>7.94</v>
       </c>
       <c r="O10" t="n">
         <v>8.52</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>13.72</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43273</v>
+        <v>43276</v>
       </c>
       <c r="H11" t="n">
-        <v>888.35</v>
+        <v>1011.75</v>
       </c>
       <c r="I11" t="n">
         <v>991.5501750243101</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K11" t="n">
-        <v>15.22</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
         <v>6.27</v>
       </c>
       <c r="M11" t="n">
-        <v>0.97</v>
+        <v>3.58</v>
       </c>
       <c r="N11" t="n">
-        <v>5.22</v>
+        <v>13.89</v>
       </c>
       <c r="O11" t="n">
         <v>-7.94</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>16.65</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43360</v>
+        <v>43361</v>
       </c>
       <c r="H12" t="n">
-        <v>1060.05</v>
+        <v>1038.15</v>
       </c>
       <c r="I12" t="n">
         <v>1043.299920817728</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K12" t="n">
-        <v>4.77</v>
+        <v>2.61</v>
       </c>
       <c r="L12" t="n">
         <v>11.32</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.12</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43406</v>
+        <v>43409</v>
       </c>
       <c r="H13" t="n">
-        <v>721.6</v>
+        <v>727.95</v>
       </c>
       <c r="I13" t="n">
         <v>721.8232926012968</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K13" t="n">
-        <v>30.49</v>
+        <v>29.88</v>
       </c>
       <c r="L13" t="n">
         <v>2.92</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>21.83</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43539</v>
+        <v>43542</v>
       </c>
       <c r="H14" t="n">
-        <v>725.5</v>
+        <v>701.85</v>
       </c>
       <c r="I14" t="n">
         <v>711.1828848290265</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.34</v>
+        <v>-3.59</v>
       </c>
       <c r="L14" t="n">
         <v>5.88</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>14.44</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43553</v>
+        <v>43556</v>
       </c>
       <c r="H15" t="n">
-        <v>716.2</v>
+        <v>776.8</v>
       </c>
       <c r="I15" t="n">
         <v>758.4617175429707</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.04</v>
+        <v>-10.68</v>
       </c>
       <c r="L15" t="n">
-        <v>5.03</v>
+        <v>12.02</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>4.37</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="O15" t="n">
         <v>-3.26</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>14.41</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43566</v>
+        <v>43567</v>
       </c>
       <c r="H16" t="n">
-        <v>694.25</v>
+        <v>680.25</v>
       </c>
       <c r="I16" t="n">
         <v>684.0496382672461</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.63</v>
+        <v>-12.43</v>
       </c>
       <c r="L16" t="n">
-        <v>10.95</v>
+        <v>12.55</v>
       </c>
       <c r="M16" t="n">
         <v>0.43</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>14.24</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43594</v>
+        <v>43595</v>
       </c>
       <c r="H17" t="n">
-        <v>580.05</v>
+        <v>650.85</v>
       </c>
       <c r="I17" t="n">
         <v>649.7330247736527</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K17" t="n">
-        <v>14.73</v>
+        <v>4.32</v>
       </c>
       <c r="L17" t="n">
         <v>2.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.64</v>
+        <v>3.95</v>
       </c>
       <c r="N17" t="n">
-        <v>3.11</v>
+        <v>12.21</v>
       </c>
       <c r="O17" t="n">
         <v>-2.02</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>16.61</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43634</v>
+        <v>43635</v>
       </c>
       <c r="H18" t="n">
-        <v>650.55</v>
+        <v>631.75</v>
       </c>
       <c r="I18" t="n">
         <v>632.3062144890205</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.05</v>
+        <v>-2.93</v>
       </c>
       <c r="L18" t="n">
         <v>8.77</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.89</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H19" t="n">
-        <v>498.85</v>
+        <v>564.35</v>
       </c>
       <c r="I19" t="n">
         <v>554.5433922331064</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K19" t="n">
-        <v>21.04</v>
+        <v>10.67</v>
       </c>
       <c r="L19" t="n">
         <v>6.32</v>
@@ -1524,7 +1751,7 @@
         <v>4.27</v>
       </c>
       <c r="N19" t="n">
-        <v>2.64</v>
+        <v>13.13</v>
       </c>
       <c r="O19" t="n">
         <v>-2.89</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>17.4</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43739</v>
+        <v>43741</v>
       </c>
       <c r="H20" t="n">
-        <v>487.45</v>
+        <v>474.6</v>
       </c>
       <c r="I20" t="n">
         <v>479.6726022911839</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
-        <v>-13.63</v>
+        <v>-15.9</v>
       </c>
       <c r="L20" t="n">
         <v>18.55</v>
       </c>
       <c r="M20" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="N20" t="n">
         <v>4.96</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>19.36</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43765</v>
+        <v>43767</v>
       </c>
       <c r="H21" t="n">
-        <v>422.6</v>
+        <v>434.1</v>
       </c>
       <c r="I21" t="n">
         <v>432.2033861653658</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K21" t="n">
-        <v>10.96</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="L21" t="n">
         <v>5.04</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>28.2</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43805</v>
+        <v>43808</v>
       </c>
       <c r="H22" t="n">
-        <v>402.05</v>
+        <v>370.25</v>
       </c>
       <c r="I22" t="n">
         <v>396.501983006394</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.38</v>
+        <v>-14.71</v>
       </c>
       <c r="L22" t="n">
-        <v>8.02</v>
+        <v>15.61</v>
       </c>
       <c r="M22" t="n">
         <v>0.96</v>
       </c>
       <c r="N22" t="n">
-        <v>3.98</v>
+        <v>7.91</v>
       </c>
       <c r="O22" t="n">
         <v>2.72</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>21.2</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43831</v>
+        <v>43832</v>
       </c>
       <c r="H23" t="n">
-        <v>368.6</v>
+        <v>407.65</v>
       </c>
       <c r="I23" t="n">
         <v>395.7682510401778</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K23" t="n">
-        <v>0.45</v>
+        <v>-10.1</v>
       </c>
       <c r="L23" t="n">
-        <v>8.49</v>
+        <v>11.74</v>
       </c>
       <c r="M23" t="n">
         <v>2.14</v>
       </c>
       <c r="N23" t="n">
-        <v>2.5</v>
+        <v>10.59</v>
       </c>
       <c r="O23" t="n">
         <v>-7.91</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>15.8</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43853</v>
+        <v>43854</v>
       </c>
       <c r="H24" t="n">
-        <v>447</v>
+        <v>399.85</v>
       </c>
       <c r="I24" t="n">
         <v>405.4585499385249</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K24" t="n">
-        <v>9.65</v>
+        <v>-1.91</v>
       </c>
       <c r="L24" t="n">
         <v>8.59</v>
       </c>
       <c r="M24" t="n">
-        <v>2.14</v>
+        <v>7.36</v>
       </c>
       <c r="N24" t="n">
-        <v>5.62</v>
+        <v>10.55</v>
       </c>
       <c r="O24" t="n">
         <v>10.59</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>21.83</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43984</v>
+        <v>43985</v>
       </c>
       <c r="H25" t="n">
-        <v>153.7</v>
+        <v>161.4</v>
       </c>
       <c r="I25" t="n">
         <v>159.6208739208697</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K25" t="n">
-        <v>61.56</v>
+        <v>59.63</v>
       </c>
       <c r="L25" t="n">
         <v>5.39</v>
@@ -1866,7 +2165,7 @@
         <v>4.99</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
       <c r="O25" t="n">
         <v>-10.55</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.97</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H26" t="n">
-        <v>303.75</v>
+        <v>278.1</v>
       </c>
       <c r="I26" t="n">
         <v>295.2990906680985</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K26" t="n">
-        <v>88.2</v>
+        <v>72.3</v>
       </c>
       <c r="L26" t="n">
         <v>4.49</v>
@@ -1923,7 +2234,7 @@
         <v>3.36</v>
       </c>
       <c r="N26" t="n">
-        <v>6.32</v>
+        <v>8.44</v>
       </c>
       <c r="O26" t="n">
         <v>5.01</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>15.1</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44202</v>
+        <v>44203</v>
       </c>
       <c r="H27" t="n">
-        <v>303.4</v>
+        <v>312.15</v>
       </c>
       <c r="I27" t="n">
         <v>311.4441468368648</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" t="n">
-        <v>-9.1</v>
+        <v>-12.24</v>
       </c>
       <c r="L27" t="n">
-        <v>12.57</v>
+        <v>14.33</v>
       </c>
       <c r="M27" t="n">
         <v>1.99</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.29</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H28" t="n">
-        <v>283.2</v>
+        <v>277.75</v>
       </c>
       <c r="I28" t="n">
         <v>281.0241393323782</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" t="n">
-        <v>-9.27</v>
+        <v>-11.02</v>
       </c>
       <c r="L28" t="n">
         <v>13.76</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>15.81</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44242</v>
+        <v>44243</v>
       </c>
       <c r="H29" t="n">
-        <v>307.3</v>
+        <v>339.45</v>
       </c>
       <c r="I29" t="n">
         <v>320.3303409648128</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K29" t="n">
-        <v>-10.64</v>
+        <v>-22.21</v>
       </c>
       <c r="L29" t="n">
-        <v>12.98</v>
+        <v>24.64</v>
       </c>
       <c r="M29" t="n">
         <v>2.6</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>10.46</v>
       </c>
       <c r="O29" t="n">
         <v>-1.92</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>16.32</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H30" t="n">
-        <v>332.7</v>
+        <v>309.7</v>
       </c>
       <c r="I30" t="n">
         <v>324.4907096075336</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.99</v>
+        <v>-8.76</v>
       </c>
       <c r="L30" t="n">
-        <v>9.119999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="M30" t="n">
         <v>1.92</v>
       </c>
       <c r="N30" t="n">
-        <v>4.55</v>
+        <v>6.91</v>
       </c>
       <c r="O30" t="n">
         <v>10.46</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>19.91</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44336</v>
+        <v>44337</v>
       </c>
       <c r="H31" t="n">
-        <v>325.35</v>
+        <v>343.95</v>
       </c>
       <c r="I31" t="n">
         <v>332.5779170446636</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.05</v>
+        <v>-11.06</v>
       </c>
       <c r="L31" t="n">
-        <v>9.279999999999999</v>
+        <v>12.59</v>
       </c>
       <c r="M31" t="n">
         <v>2.09</v>
       </c>
       <c r="N31" t="n">
-        <v>4.85</v>
+        <v>5.72</v>
       </c>
       <c r="O31" t="n">
         <v>-6.91</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>13.13</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44361</v>
+        <v>44362</v>
       </c>
       <c r="H32" t="n">
-        <v>641.9</v>
+        <v>609.8</v>
       </c>
       <c r="I32" t="n">
         <v>620.3646866298075</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K32" t="n">
-        <v>86.63</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="L32" t="n">
         <v>5.83</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>21.31</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44526</v>
+        <v>44529</v>
       </c>
       <c r="H33" t="n">
-        <v>413.8</v>
+        <v>434.45</v>
       </c>
       <c r="I33" t="n">
         <v>422.4601731939591</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K33" t="n">
-        <v>32.14</v>
+        <v>28.76</v>
       </c>
       <c r="L33" t="n">
         <v>6.59</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>7</v>
+      </c>
+      <c r="U33" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>11.43</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H34" t="n">
-        <v>427.2</v>
+        <v>405.9</v>
       </c>
       <c r="I34" t="n">
         <v>422.1240214360797</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.67</v>
+        <v>-6.57</v>
       </c>
       <c r="L34" t="n">
-        <v>1.67</v>
+        <v>6.57</v>
       </c>
       <c r="M34" t="n">
-        <v>1.63</v>
+        <v>4.21</v>
       </c>
       <c r="N34" t="n">
         <v>4.99</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>17.81</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44609</v>
+        <v>44610</v>
       </c>
       <c r="H35" t="n">
-        <v>360.7</v>
+        <v>372.9</v>
       </c>
       <c r="I35" t="n">
         <v>372.1108331303365</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K35" t="n">
-        <v>11.14</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L35" t="n">
         <v>8.91</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>18.21</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H36" t="n">
-        <v>308.25</v>
+        <v>298.55</v>
       </c>
       <c r="I36" t="n">
         <v>308.0018073994123</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K36" t="n">
-        <v>-17.34</v>
+        <v>-19.94</v>
       </c>
       <c r="L36" t="n">
-        <v>18.18</v>
+        <v>20.26</v>
       </c>
       <c r="M36" t="n">
         <v>6.09</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>14.38</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44720</v>
+        <v>44721</v>
       </c>
       <c r="H37" t="n">
-        <v>285.9</v>
+        <v>329.2</v>
       </c>
       <c r="I37" t="n">
         <v>301.7422068267227</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K37" t="n">
-        <v>4.24</v>
+        <v>-10.27</v>
       </c>
       <c r="L37" t="n">
-        <v>4.82</v>
+        <v>13.47</v>
       </c>
       <c r="M37" t="n">
         <v>3.33</v>
       </c>
       <c r="N37" t="n">
-        <v>4.6</v>
+        <v>15.15</v>
       </c>
       <c r="O37" t="n">
         <v>-3.15</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>19.53</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H38" t="n">
-        <v>276.85</v>
+        <v>267.45</v>
       </c>
       <c r="I38" t="n">
         <v>268.8939312233191</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K38" t="n">
-        <v>-15.9</v>
+        <v>-18.76</v>
       </c>
       <c r="L38" t="n">
-        <v>18.64</v>
+        <v>19.99</v>
       </c>
       <c r="M38" t="n">
         <v>2.97</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>18.94</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44784</v>
+        <v>44785</v>
       </c>
       <c r="H39" t="n">
-        <v>288.4</v>
+        <v>302.9</v>
       </c>
       <c r="I39" t="n">
         <v>297.6885409669788</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.83</v>
+        <v>-13.25</v>
       </c>
       <c r="L39" t="n">
-        <v>13.03</v>
+        <v>14.4</v>
       </c>
       <c r="M39" t="n">
         <v>2.43</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.66</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H40" t="n">
-        <v>335</v>
+        <v>315.3</v>
       </c>
       <c r="I40" t="n">
         <v>321.5376788735432</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K40" t="n">
-        <v>10.6</v>
+        <v>4.09</v>
       </c>
       <c r="L40" t="n">
         <v>5.38</v>
@@ -2721,7 +3200,7 @@
         <v>2.55</v>
       </c>
       <c r="N40" t="n">
-        <v>3.19</v>
+        <v>5.88</v>
       </c>
       <c r="O40" t="n">
         <v>5.03</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>17.92</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44853</v>
+        <v>44854</v>
       </c>
       <c r="H41" t="n">
-        <v>352.15</v>
+        <v>367.8</v>
       </c>
       <c r="I41" t="n">
         <v>359.8938430915888</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>-11.69</v>
+        <v>-16.65</v>
       </c>
       <c r="L41" t="n">
-        <v>12.56</v>
+        <v>17.41</v>
       </c>
       <c r="M41" t="n">
         <v>2.24</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>14.93</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44998</v>
+        <v>44999</v>
       </c>
       <c r="H42" t="n">
-        <v>484.6</v>
+        <v>432.65</v>
       </c>
       <c r="I42" t="n">
         <v>465.1239952455742</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K42" t="n">
-        <v>31.76</v>
+        <v>17.63</v>
       </c>
       <c r="L42" t="n">
         <v>6.55</v>
@@ -2835,7 +3338,7 @@
         <v>1.58</v>
       </c>
       <c r="N42" t="n">
-        <v>7.92</v>
+        <v>10.72</v>
       </c>
       <c r="O42" t="n">
         <v>4.44</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>6</v>
+      </c>
+      <c r="U42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>23.95</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45019</v>
+        <v>45021</v>
       </c>
       <c r="H43" t="n">
-        <v>448</v>
+        <v>463.15</v>
       </c>
       <c r="I43" t="n">
         <v>463.1073997385412</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.55</v>
+        <v>-7.05</v>
       </c>
       <c r="L43" t="n">
         <v>13.27</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>17.4</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45134</v>
+        <v>45135</v>
       </c>
       <c r="H44" t="n">
-        <v>637.45</v>
+        <v>617.05</v>
       </c>
       <c r="I44" t="n">
         <v>623.3006821411054</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K44" t="n">
-        <v>37.63</v>
+        <v>33.23</v>
       </c>
       <c r="L44" t="n">
         <v>12.19</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>14.14</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45181</v>
+        <v>45182</v>
       </c>
       <c r="H45" t="n">
-        <v>667.95</v>
+        <v>684.1</v>
       </c>
       <c r="I45" t="n">
         <v>683.9613392465239</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.25</v>
+        <v>-10.87</v>
       </c>
       <c r="L45" t="n">
         <v>12.47</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.26</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45320</v>
+        <v>45321</v>
       </c>
       <c r="H46" t="n">
-        <v>791.25</v>
+        <v>763.15</v>
       </c>
       <c r="I46" t="n">
         <v>770.820049166558</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K46" t="n">
-        <v>15.66</v>
+        <v>11.56</v>
       </c>
       <c r="L46" t="n">
         <v>4.82</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>19.61</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H47" t="n">
-        <v>629.85</v>
+        <v>749.3</v>
       </c>
       <c r="I47" t="n">
         <v>711.3444824047849</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K47" t="n">
-        <v>17.47</v>
+        <v>1.81</v>
       </c>
       <c r="L47" t="n">
         <v>10.8</v>
       </c>
       <c r="M47" t="n">
-        <v>1.61</v>
+        <v>3.36</v>
       </c>
       <c r="N47" t="n">
-        <v>5.7</v>
+        <v>18.96</v>
       </c>
       <c r="O47" t="n">
         <v>-3.55</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>20.65</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45442</v>
+        <v>45443</v>
       </c>
       <c r="H48" t="n">
-        <v>745.4</v>
+        <v>722.9</v>
       </c>
       <c r="I48" t="n">
         <v>731.8823831035932</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.52</v>
+        <v>-3.52</v>
       </c>
       <c r="L48" t="n">
         <v>13.12</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>12.19</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45453</v>
+        <v>45454</v>
       </c>
       <c r="H49" t="n">
-        <v>764.1</v>
+        <v>808.15</v>
       </c>
       <c r="I49" t="n">
         <v>783.1034482660435</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.7</v>
+        <v>-11.79</v>
       </c>
       <c r="L49" t="n">
-        <v>7.07</v>
+        <v>13.23</v>
       </c>
       <c r="M49" t="n">
         <v>3.74</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>15.88</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H50" t="n">
-        <v>971.8</v>
+        <v>938.75</v>
       </c>
       <c r="I50" t="n">
         <v>959.1552691120058</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K50" t="n">
-        <v>20.25</v>
+        <v>16.16</v>
       </c>
       <c r="L50" t="n">
         <v>8.279999999999999</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>16.83</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H51" t="n">
-        <v>860.8</v>
+        <v>872.95</v>
       </c>
       <c r="I51" t="n">
         <v>864.2731006958959</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K51" t="n">
-        <v>8.300000000000001</v>
+        <v>7.01</v>
       </c>
       <c r="L51" t="n">
         <v>10.25</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>6</v>
+      </c>
+      <c r="U51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.99</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H52" t="n">
-        <v>1050.2</v>
+        <v>1010.4</v>
       </c>
       <c r="I52" t="n">
         <v>1035.563120201105</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K52" t="n">
-        <v>20.3</v>
+        <v>15.75</v>
       </c>
       <c r="L52" t="n">
         <v>3.09</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>10.86</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="H53" t="n">
-        <v>812.35</v>
+        <v>830.15</v>
       </c>
       <c r="I53" t="n">
         <v>824.7011350207752</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K53" t="n">
-        <v>19.6</v>
+        <v>17.84</v>
       </c>
       <c r="L53" t="n">
         <v>4.22</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.86</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="H54" t="n">
-        <v>930.55</v>
+        <v>860.25</v>
       </c>
       <c r="I54" t="n">
         <v>929.9241530171099</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K54" t="n">
-        <v>12.09</v>
+        <v>3.63</v>
       </c>
       <c r="L54" t="n">
         <v>2.31</v>
@@ -3519,7 +4166,7 @@
         <v>0.89</v>
       </c>
       <c r="N54" t="n">
-        <v>4.81</v>
+        <v>7.55</v>
       </c>
       <c r="O54" t="n">
         <v>2.19</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>13.76</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H55" t="n">
-        <v>817</v>
+        <v>873.3</v>
       </c>
       <c r="I55" t="n">
         <v>832.0538318537136</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K55" t="n">
-        <v>5.03</v>
+        <v>-1.52</v>
       </c>
       <c r="L55" t="n">
         <v>7.53</v>
@@ -3576,7 +4235,7 @@
         <v>4.21</v>
       </c>
       <c r="N55" t="n">
-        <v>4.74</v>
+        <v>6.89</v>
       </c>
       <c r="O55" t="n">
         <v>-7.55</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>13.7</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="H56" t="n">
-        <v>1030.5</v>
+        <v>1003</v>
       </c>
       <c r="I56" t="n">
         <v>1006.970291513563</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K56" t="n">
-        <v>18</v>
+        <v>14.85</v>
       </c>
       <c r="L56" t="n">
         <v>4.4</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>12.03</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="H57" t="n">
-        <v>1051.8</v>
+        <v>1055.6</v>
       </c>
       <c r="I57" t="n">
         <v>1053.002845929869</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.87</v>
+        <v>-5.24</v>
       </c>
       <c r="L57" t="n">
         <v>7.67</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H58" t="n">
-        <v>1138.5</v>
+        <v>1094.5</v>
       </c>
       <c r="I58" t="n">
         <v>1100.877733588426</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K58" t="n">
-        <v>7.85</v>
+        <v>3.69</v>
       </c>
       <c r="L58" t="n">
         <v>2.97</v>
@@ -3747,7 +4442,7 @@
         <v>1.11</v>
       </c>
       <c r="N58" t="n">
-        <v>3.38</v>
+        <v>3.86</v>
       </c>
       <c r="O58" t="n">
         <v>0.36</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>10.77</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="H59" t="n">
-        <v>1158</v>
+        <v>1200</v>
       </c>
       <c r="I59" t="n">
         <v>1180.973682407964</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.8</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>7.32</v>
+        <v>10.18</v>
       </c>
       <c r="M59" t="n">
         <v>1.06</v>
       </c>
       <c r="N59" t="n">
-        <v>2.62</v>
+        <v>3.63</v>
       </c>
       <c r="O59" t="n">
         <v>-3.86</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>10.05</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="H60" t="n">
-        <v>1138.5</v>
+        <v>1089.1</v>
       </c>
       <c r="I60" t="n">
         <v>1108.367060683189</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K60" t="n">
-        <v>-5.12</v>
+        <v>-9.24</v>
       </c>
       <c r="L60" t="n">
-        <v>6.68</v>
+        <v>10.45</v>
       </c>
       <c r="M60" t="n">
         <v>1.22</v>
       </c>
       <c r="N60" t="n">
-        <v>2.02</v>
+        <v>4.34</v>
       </c>
       <c r="O60" t="n">
         <v>3.63</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3921,6 +4652,14 @@
       <c r="Q61" t="n">
         <v>4</v>
       </c>
+      <c r="R61" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8131,7 +8870,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.7</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="6">
@@ -8141,7 +8880,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -8151,7 +8890,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">
@@ -8161,7 +8900,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -8171,7 +8910,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.5</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="10">
@@ -8181,7 +8920,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132.4</v>
+        <v>134.2</v>
       </c>
     </row>
     <row r="11">
@@ -8191,7 +8930,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -8201,7 +8940,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -8211,7 +8950,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="14">
@@ -8221,7 +8960,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.44</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="15">
@@ -8231,7 +8970,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.96</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="16">
@@ -8241,7 +8980,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.83</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="17">
@@ -8251,7 +8990,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>88.2</v>
+        <v>77.29000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -8261,7 +9000,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.2</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="19">
@@ -8271,7 +9010,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.02</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -8281,7 +9020,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.53</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="21">
@@ -8291,7 +9030,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.64</v>
+        <v>24.64</v>
       </c>
     </row>
     <row r="22">
@@ -8301,7 +9040,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -8311,7 +9050,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -8321,7 +9060,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.69</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="25">
@@ -8341,7 +9080,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.22</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="27">
@@ -8351,7 +9090,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.81</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="28">
@@ -8361,7 +9100,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
